--- a/my-work (outputs)/internal/2026.09.28 - Internal - Cadence Turn-On Tracker.xlsx
+++ b/my-work (outputs)/internal/2026.09.28 - Internal - Cadence Turn-On Tracker.xlsx
@@ -499,28 +499,28 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kate decides when a cadence switches on. Nothing is live until it has its Build, at least Touch 1, and a send schedule the builds stay ahead of (Kate, 2026.09.29). Only ABM is on today.</t>
+          <t>Kate decides when a cadence switches on. Nothing is live until it has its Build, at least Touch 1, and a send schedule the builds stay ahead of (Kate, 2026.09.29). Live today: ABM, Business Transformation (10/1) and Sales Intelligence (9/30).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>The math: spacing from the engagement spec, Path A. Touches send on Days 1, 4, 8, 11, 16 (Days 1, 4, 9, 12, 17 for Business Transformation and Market Expansion). 'Earliest safe' is the first day nobody could reach a touch built less than 2 days earlier. Check the real step delays in Zoho first.</t>
+          <t>The math (Jack, 2026.10.05): new cadences follow the BT and SI pattern, Touch 1 on switch-on, then every 7 days. Touch 2 must be built by switch-on +5 days, Touch 3 by +12, Touch 4 by +19, Touch 5 by +26. 'Earliest safe' is the first day every touch is built at least 2 days ahead. Check the real step delays in Zoho first.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Before any switch-on: start contacts fresh at Touch 1 (never resume a paused cadence mid-sequence), set enrollment exclusions, and make sure no template anywhere says [PLACEHOLDER].</t>
+          <t>Before any switch-on: Ignite Beta Hold suppression on the view and in un-enroll criteria, un-enroll on reply and Meeting Booked, a fresh Auto-Enroll cadence (never reactivate an old one), everyone starts at Touch 1, no [PLACEHOLDER] anywhere, all five templates test-sent to Mr. Testy, Kate's yes on the day.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Dates follow Master Schedule update #4 (2026.09.29): Market Expansion and Site Visit Targeting built from scratch, Site Visit Targeting ahead of Revenue Intelligence (Jack's order). Target switch-on dates are Kate's (9/29). Janice watches the Switch-On Checklist tab; if a topic's list isn't done by its target morning, she moves the target out one week (never earlier than Earliest safe) and says so in one line.</t>
+          <t>Dates follow Master Schedule Update #11 (2026.10.05): Jack's build order, approved by Kate 10/5. Pairs build in rounds (RI+ME, ST+RM, SPM+B2B, BD+DM), BT and SI Touch 3 to 5 first. All builds done Thu 11/19. Touch columns show the day each touch is built. Janice watches the Switch-On Checklist tab; if a topic's list isn't done by its target morning, she moves the target out one week (never earlier than Earliest safe) and says so in one line.</t>
         </is>
       </c>
     </row>
@@ -594,27 +594,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>10/5</t>
+          <t>10/8 (copy + GIF in Zoho 10/6, test sent to Mr. Testy; independent readback pending)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>10/14</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>10/20</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Tue 10/6</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Rebuild Touches 3 to 5 (still hold the old 'silent saboteur' copy). Set enrollment exclusions. 324 existing contacts: INCLUDE, start fresh at Touch 1 (Kate, 9/29). Test on Mr. Testy.</t>
+          <t>Live cadence. Touches 3 to 5 hold holding copy; the real copy replaces it before each fires (Thu 10/15, 10/22, 10/29). Touch 3 uses the Stage 3 'navigator' message locked 10/1.</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Tue 10/6 (set 9/29)</t>
+          <t>Live since Thu 10/1</t>
         </is>
       </c>
     </row>
@@ -651,22 +651,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>10/14</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>10/20</t>
+          <t>10/21</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Thu 10/8</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Paste final Touch 1 and 2 copy with GIFs (media 913, 924). Enrollment: ALL 50 tagged contacts (Kate, 9/29), existing records included. Test on Mr. Testy. Report page 915 publishes on switch-on day.</t>
+          <t>Live cadence. Touches 3 to 5 hold holding copy; the real copy replaces it before each fires (Thu 10/15, 10/22, 10/29).</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Thu 10/8 (set 9/29)</t>
+          <t>Live since Wed 9/30</t>
         </is>
       </c>
     </row>
@@ -688,22 +688,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>9/30 (Build 9/29)</t>
+          <t>10/12 (Build 10/9)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>10/7</t>
+          <t>10/13</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>10/15</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>10/21</t>
+          <t>10/22</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>New build from scratch. Leave the old paused August cadence off.</t>
+          <t>New build from scratch. Leave the old paused August cadence off. The Wed 10/7 "Touch 2" slot was a mistake (no Build yet) and became Build Revenue Intelligence.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -726,7 +726,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J9" s="7" t="n"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Tue 10/27 (Kate approved 10/5)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -776,7 +780,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Tue 10/20 (set 9/30)</t>
+          <t>Tue 10/20 (set 9/30, unchanged)</t>
         </is>
       </c>
     </row>
@@ -788,37 +792,37 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>11/2 (Build 10/29)</t>
+          <t>10/9 (Build 10/7)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>11/3</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>11/4</t>
+          <t>10/15</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>11/5</t>
+          <t>10/21</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>11/9</t>
+          <t>10/26</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Thu 11/5</t>
+          <t>Mon 10/12</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>13 contacts. Exclude the 3 McKinsey contacts.</t>
+          <t>13 contacts. Exclude the 3 McKinsey contacts. Switch-on checklist runs Mon 10/12. PM Hotel Group is surging on this topic, so the Ignite Beta Hold must be in place first.</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -826,139 +830,163 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J11" s="7" t="n"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Tue 10/13 (Kate approved 10/5). Slips to Tue 10/20 if the Beta Hold suppression is not built in Zoho by Mon 10/12</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Sales Transformation</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>11/11 (Build 11/10)</t>
+          <t>10/19 (Build 10/16)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>10/22</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>10/27</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/30</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>11/2</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Sat 11/14</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
+          <t>Tue 10/20</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Old Touch 1 went to 100 contacts on 9/28 (86 delivered). Start them fresh at Touch 1 of the new build or hold them out: Kate decides at switch-on.</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J12" s="7" t="n"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Tue 11/3 (Kate approved 10/5)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Sales Performance Management</t>
+          <t>Revenue Management</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>11/23 (Build 11/19)</t>
+          <t>10/20 (Build 10/19)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>11/23</t>
+          <t>10/23</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>11/24</t>
+          <t>10/27</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>11/24</t>
+          <t>11/2</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>11/3</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Thu 11/26</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>Wed 10/21</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Role filter: Director+/VP+ commercial strategy only. Pairs with Sales Transformation (same commercial leader).</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J13" s="7" t="n"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Tue 11/10 (Kate approved 10/5)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Sales Transformation</t>
+          <t>Sales Performance Management</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>11/26 (Build 11/25)</t>
+          <t>10/29 (Build 10/28)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>11/3</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/4</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/9</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Sun 11/29</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
+          <t>Fri 10/30</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J14" s="7" t="n"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Tue 11/17 (Kate approved 10/5)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -968,125 +996,137 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>12/1 (Build 11/30)</t>
+          <t>10/29 (Build 10/28)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>12/2</t>
+          <t>11/4</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>12/3</t>
+          <t>11/5</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>12/7</t>
+          <t>11/9</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>12/8</t>
+          <t>11/11</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Fri 12/4</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>Mon 11/2</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Not Thanksgiving week: a Tue 11/24 first touch lands in the emptiest inboxes of the quarter.</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J15" s="7" t="n"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Tue 12/1 (Kate approved 10/5)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Digital Marketing</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>12/10 (Build 12/9)</t>
+          <t>11/10 (Build 11/5)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/12</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/16</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>11/17</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>11/18</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Mon 12/14</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr"/>
+          <t>Wed 11/11</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J16" s="7" t="n"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Tue 12/8 (Kate approved 10/5)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Revenue Management</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>12/21 (Build 12/21)</t>
+          <t>11/10 (Build 11/6)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>12/22</t>
+          <t>11/13</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>12/22</t>
+          <t>11/16</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>12/23</t>
+          <t>11/17</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>12/23</t>
+          <t>11/19</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>After the holidays</t>
+          <t>Wed 11/11</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Role filter: Director+/VP+ commercial strategy only.</t>
+          <t>Biggest pool (711 tagged). Build as a fresh cadence and leave the old one off: it still holds Ongoing enrollments (incl. 5 Noble Corporation contacts) that would fire old Phase 1 copy.</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1094,7 +1134,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J17" s="7" t="n"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Tue 1/5/2027 (Kate approved 10/5)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A7:I18"/>
@@ -1113,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1923,6 +1967,52 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>All new cadences</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Ignite Beta Hold suppression in Zoho: checkbox on Contacts and Leads, workflow rule on email domain, mass-tick the 11 existing records, view criterion on every auto-enroll view, un-enroll criterion on every live cadence, six companies excluded in ZoomInfo workflows</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Kate in Zoho (about 45 min)</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Due Mon 10/12, or Revenue Intelligence slips to Tue 10/20. Key on email domain, not account name. Spec: Session 3B-ii - GTM Sales/2026.10.05 - Internal - Cadence Build Order and Suppression Check.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Revenue Intelligence</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Switch-on checklist complete (suppression, un-enroll on reply and Meeting Booked, fresh Auto-Enroll cadence, no [PLACEHOLDER], 5 templates to Mr. Testy)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Kate + Zoho screens</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Runs Mon 10/12 with Touch 2. Target switch-on Tue 10/13.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/my-work (outputs)/internal/2026.09.28 - Internal - Cadence Turn-On Tracker.xlsx
+++ b/my-work (outputs)/internal/2026.09.28 - Internal - Cadence Turn-On Tracker.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Tue 10/13 (Kate approved 10/5). Slips to Tue 10/20 if the Beta Hold suppression is not built in Zoho by Mon 10/12</t>
+          <t>Tue 10/20 (moved from Tue 10/13 on 10/11: Kate sick Thu-Fri, Build RI now Tue 10/13 and Touch 1 Thu 10/15). Slips again if the Ignite Beta Hold suppression isn't built.</t>
         </is>
       </c>
     </row>
@@ -1181,6 +1181,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1986,7 +1987,7 @@
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Due Mon 10/12, or Revenue Intelligence slips to Tue 10/20. Key on email domain, not account name. Spec: Session 3B-ii - GTM Sales/2026.10.05 - Internal - Cadence Build Order and Suppression Check.md</t>
+          <t>Due Mon 10/12, or Revenue Intelligence slips to Tue 10/20. Key on email domain, not account name. Spec: Session 3B-ii - GTM Sales/2026.10.05 - Internal - Cadence Build Order and Suppression Check.md Scheduled Sun 10/11 12:00 to 12:45 CT (Janice, 10/11).</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2010,7 @@
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Runs Mon 10/12 with Touch 2. Target switch-on Tue 10/13.</t>
+          <t>Moved 10/11: runs with RI Touch 2 ahead of the new Tue 10/20 target.</t>
         </is>
       </c>
     </row>
